--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post FET_HRM-2031-0472/panel_11/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post FET_HRM-2031-0472/panel_11/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,17 +434,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -456,26 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.46862</v>
+        <v>17.47427</v>
       </c>
       <c r="D2" t="n">
-        <v>16.51542</v>
+        <v>16.82351</v>
       </c>
       <c r="E2" t="n">
-        <v>17.16025</v>
+        <v>17.35985</v>
       </c>
       <c r="F2" t="n">
-        <v>22.48746</v>
+        <v>43.28891</v>
       </c>
       <c r="G2" t="n">
-        <v>22.13793</v>
+        <v>0.05135</v>
       </c>
       <c r="H2" t="n">
-        <v>35.04884</v>
+        <v>1.90471</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.3526</v>
+        <v>17.28715</v>
       </c>
       <c r="D3" t="n">
-        <v>16.71342</v>
+        <v>17.17649</v>
       </c>
       <c r="E3" t="n">
-        <v>17.12727</v>
+        <v>17.19869</v>
       </c>
       <c r="F3" t="n">
-        <v>22.08346</v>
+        <v>43.98523</v>
       </c>
       <c r="G3" t="n">
-        <v>22.4582</v>
+        <v>0.05082</v>
       </c>
       <c r="H3" t="n">
-        <v>34.58852</v>
+        <v>1.86444</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.99917</v>
+        <v>17.19496</v>
       </c>
       <c r="D4" t="n">
-        <v>16.69754</v>
+        <v>16.94041</v>
       </c>
       <c r="E4" t="n">
-        <v>17.1551</v>
+        <v>17.1337</v>
       </c>
       <c r="F4" t="n">
-        <v>22.379</v>
+        <v>44.31562</v>
       </c>
       <c r="G4" t="n">
-        <v>22.30912</v>
+        <v>0.05252</v>
       </c>
       <c r="H4" t="n">
-        <v>35.73807</v>
+        <v>1.90923</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.05</v>
+        <v>17.42734</v>
       </c>
       <c r="D5" t="n">
-        <v>16.39907</v>
+        <v>16.94737</v>
       </c>
       <c r="E5" t="n">
-        <v>16.48808</v>
+        <v>16.98527</v>
       </c>
       <c r="F5" t="n">
-        <v>22.10807</v>
+        <v>44.34534</v>
       </c>
       <c r="G5" t="n">
-        <v>22.18316</v>
+        <v>0.05269</v>
       </c>
       <c r="H5" t="n">
-        <v>35.473</v>
+        <v>1.88137</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.44116</v>
+        <v>17.48825</v>
       </c>
       <c r="D6" t="n">
-        <v>16.31914</v>
+        <v>17.14959</v>
       </c>
       <c r="E6" t="n">
-        <v>16.85213</v>
+        <v>17.22883</v>
       </c>
       <c r="F6" t="n">
-        <v>22.26434</v>
+        <v>44.35237</v>
       </c>
       <c r="G6" t="n">
-        <v>22.96665</v>
+        <v>0.05198</v>
       </c>
       <c r="H6" t="n">
-        <v>35.12785</v>
+        <v>1.88829</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.98515</v>
+        <v>17.62539</v>
       </c>
       <c r="D7" t="n">
-        <v>16.48807</v>
+        <v>17.11582</v>
       </c>
       <c r="E7" t="n">
-        <v>17.25325</v>
+        <v>17.31526</v>
       </c>
       <c r="F7" t="n">
-        <v>22.59897</v>
+        <v>43.60274</v>
       </c>
       <c r="G7" t="n">
-        <v>22.65904</v>
+        <v>0.05198</v>
       </c>
       <c r="H7" t="n">
-        <v>34.5511</v>
+        <v>1.88206</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.35947</v>
+        <v>17.2506</v>
       </c>
       <c r="D8" t="n">
-        <v>16.47511</v>
+        <v>17.03219</v>
       </c>
       <c r="E8" t="n">
-        <v>16.77958</v>
+        <v>17.20563</v>
       </c>
       <c r="F8" t="n">
-        <v>22.56627</v>
+        <v>44.61099</v>
       </c>
       <c r="G8" t="n">
-        <v>22.67812</v>
+        <v>0.05229</v>
       </c>
       <c r="H8" t="n">
-        <v>34.78356</v>
+        <v>1.86487</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.04969</v>
+        <v>17.15765</v>
       </c>
       <c r="D9" t="n">
-        <v>16.2428</v>
+        <v>17.08598</v>
       </c>
       <c r="E9" t="n">
-        <v>16.44112</v>
+        <v>17.14824</v>
       </c>
       <c r="F9" t="n">
-        <v>21.92013</v>
+        <v>43.995</v>
       </c>
       <c r="G9" t="n">
-        <v>22.48127</v>
+        <v>0.05081</v>
       </c>
       <c r="H9" t="n">
-        <v>35.56555</v>
+        <v>1.83697</v>
       </c>
     </row>
     <row r="10">
@@ -660,63 +660,48 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.44205</v>
+        <v>17.3122</v>
       </c>
       <c r="D10" t="n">
-        <v>16.60605</v>
+        <v>17.2041</v>
       </c>
       <c r="E10" t="n">
-        <v>16.92313</v>
+        <v>17.26597</v>
       </c>
       <c r="F10" t="n">
-        <v>22.34972</v>
+        <v>43.40335</v>
       </c>
       <c r="G10" t="n">
-        <v>21.88913</v>
+        <v>0.0527</v>
       </c>
       <c r="H10" t="n">
-        <v>35.13704</v>
+        <v>1.85563</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -728,32 +713,8 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>roughness</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.76698</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.08203000000000001</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.6363</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.9966699999999999</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.11537</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.00781</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.09725</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.13049</v>
+          <t>Trace 1</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -762,30 +723,6 @@
           <t>Unit 8</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>0.7713100000000001</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.08230999999999999</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.62653</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.98576</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.11241</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.0078</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.09662</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.1317</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -793,30 +730,6 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>0.77519</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.08216</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.62177</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1.00408</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.00793</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.09752</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.12883</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -824,30 +737,6 @@
           <t>Unit 4</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>0.7467200000000001</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.08295</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.61988</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1.01744</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.11074</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.00771</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.09612999999999999</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.12738</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -855,30 +744,6 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>0.76929</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.08329</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.63019</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.9932800000000001</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.11325</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.00774</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.09303</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.13212</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -886,30 +751,6 @@
           <t>Unit 6</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>0.78395</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.08149000000000001</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.62899</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.99619</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.11345</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.00767</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.09558</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.13266</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -917,30 +758,6 @@
           <t>Unit 1</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>0.76986</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.08212</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.63093</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.99921</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.11048</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.00795</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.09487</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.13294</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -948,30 +765,6 @@
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>0.77868</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.08361</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.62897</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1.00004</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.11349</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.007939999999999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.09569</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.12853</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -979,29 +772,331 @@
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>0.77624</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.0832</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.62396</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.98385</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.11363</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.00781</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.09452000000000001</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.13265</v>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>0.75491</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.08185000000000001</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.63492</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.98556</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.11163</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.0969</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.12943</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.77227</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.08384999999999999</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.6259</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.9732499999999999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.11272</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.007820000000000001</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.09687</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.13097</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.77933</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.08396000000000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.62805</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9958</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.11249</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.00804</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.09408</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.12949</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.77335</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.08499</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6296</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.99727</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.1112</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.00776</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.09583999999999999</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.1282</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0.77411</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.08326</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.62079</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.00256</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.11376</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.00778</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.09597</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.13343</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0.77728</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.08406</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.62967</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.99383</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.11266</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.00795</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.09707</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.12853</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7768699999999999</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.08356</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.6248899999999999</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.98663</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.11072</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.09649000000000001</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.13028</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.75254</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.08368</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6321099999999999</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.9857900000000001</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.11031</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.00769</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.0954</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.12884</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7609900000000001</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.08377</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.62448</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.00095</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.11277</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.00795</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.09598</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.12949</v>
       </c>
     </row>
   </sheetData>
